--- a/TASTI_SYNTHETIC/PnoTOPT.xlsx
+++ b/TASTI_SYNTHETIC/PnoTOPT.xlsx
@@ -441,56 +441,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28X150B127</t>
+          <t>89V924U181</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TOPT-962</t>
+          <t>TOPT-700</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>STEP 2</t>
+          <t>STEP 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Performance</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19F540G508</t>
+          <t>25D871S921</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TOPT-817</t>
+          <t>TOPT-373</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>STEP 1</t>
+          <t>STEP 3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Performance</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>49L153N369</t>
+          <t>97Y195W199</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TOPT-168</t>
+          <t>TOPT-380</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,19 +500,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Exterior</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>57B882T410</t>
+          <t>26P115W528</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TOPT-784</t>
+          <t>TOPT-512</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,19 +522,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Exterior</t>
+          <t>Comfort</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>42H991S513</t>
+          <t>48P763Z436</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TOPT-722</t>
+          <t>TOPT-394</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -544,24 +544,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Comfort</t>
+          <t>Exterior</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>67B846Q378</t>
+          <t>38A884P434</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TOPT-668</t>
+          <t>TOPT-843</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>STEP 2</t>
+          <t>STEP 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -573,12 +573,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>71A540Y782</t>
+          <t>82Z492C536</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOPT-170</t>
+          <t>TOPT-984</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,34 +595,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13Q711N389</t>
+          <t>28Q472X142</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOPT-570</t>
+          <t>TOPT-924</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>STEP 1</t>
+          <t>STEP 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Exterior</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>70L953W917</t>
+          <t>63F416W427</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOPT-879</t>
+          <t>TOPT-883</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -632,19 +632,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Performance</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>47S229U778</t>
+          <t>55X693W912</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TOPT-379</t>
+          <t>TOPT-214</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,41 +654,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Comfort</t>
+          <t>Safety</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>79A509G922</t>
+          <t>84Z132L329</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOPT-632</t>
+          <t>TOPT-757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STEP 2</t>
+          <t>STEP 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Exterior</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>57Q493C657</t>
+          <t>41E185V152</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOPT-374</t>
+          <t>TOPT-438</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,29 +698,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Exterior</t>
+          <t>Safety</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>64K665K693</t>
+          <t>59B257Z511</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TOPT-951</t>
+          <t>TOPT-709</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>STEP 2</t>
+          <t>STEP 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Exterior</t>
+          <t>Performance</t>
         </is>
       </c>
     </row>
